--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="499">
   <si>
     <t>Filename</t>
   </si>
@@ -808,685 +808,709 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9631,0.0024,0.0190,0.0016</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0002,0.9997</t>
-  </si>
-  <si>
-    <t>0.9947,0.0004,0.0000,0.0015</t>
-  </si>
-  <si>
-    <t>0.0032,0.0000,0.0000,0.9994</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9725,0.0025,0.0088,0.0031</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.9799,0.0015,0.0001,0.0067</t>
+  </si>
+  <si>
+    <t>0.0066,0.0000,0.0000,0.9988</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5591,0.0013,0.5045,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0010,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.4890,0.0003,0.7011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0029,0.0002,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.9938,0.0001,0.0047,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9969,0.0059,0.0001</t>
+  </si>
+  <si>
+    <t>0.0355,0.9653,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.9940,0.0090,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9792,0.0001,0.0170,0.0001</t>
+  </si>
+  <si>
+    <t>0.8566,0.0051,0.1331,0.0006</t>
+  </si>
+  <si>
+    <t>0.0055,0.0016,0.9910,0.0004</t>
+  </si>
+  <si>
+    <t>0.0121,0.0038,0.9744,0.0023</t>
+  </si>
+  <si>
+    <t>0.0156,0.0001,0.9906,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9993,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0006</t>
+  </si>
+  <si>
+    <t>0.1997,0.7446,0.0092,0.0003</t>
+  </si>
+  <si>
+    <t>0.5190,0.0225,0.3049,0.0025</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0031</t>
+  </si>
+  <si>
+    <t>0.0382,0.5291,0.1531,0.0002</t>
+  </si>
+  <si>
+    <t>0.9862,0.0089,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.5799,0.0030,0.4208,0.0032</t>
+  </si>
+  <si>
+    <t>0.0320,0.9667,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.9924,0.0072,0.0008</t>
+  </si>
+  <si>
+    <t>0.1117,0.0784,0.5408,0.0111</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.9975,0.0012</t>
+  </si>
+  <si>
+    <t>0.0220,0.0016,0.9708,0.0007</t>
+  </si>
+  <si>
+    <t>0.0055,0.0003,0.9918,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.0011,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9980,0.0041,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.8310,0.0010,0.9200</t>
+  </si>
+  <si>
+    <t>0.0003,0.9990,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0926,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0645,0.0036,0.9317,0.0024</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0007,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0050,0.0035,0.9928,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0007,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0011,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9937,0.9083,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0010,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0063,0.9993,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9529,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.9932,0.0051,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0956,0.0019,0.9378,0.0001</t>
+  </si>
+  <si>
+    <t>0.9742,0.0118,0.0063,0.0007</t>
+  </si>
+  <si>
+    <t>0.0013,0.0022,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9900,0.9915,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.5666,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.4356,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9948,0.9664,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0112,0.9988</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0006,0.9997</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.0004,0.9995</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9973,0.7574,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.8783,0.9161,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.4806,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.4437,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9971,0.5914,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0093,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.0030,0.9944,0.0005</t>
+  </si>
+  <si>
+    <t>0.9971,0.0001,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9995,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.9970,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9963,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.4354,0.5937,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.1141,0.0143,0.8493,0.0014</t>
+  </si>
+  <si>
+    <t>0.9283,0.0008,0.0782,0.0002</t>
+  </si>
+  <si>
+    <t>0.2124,0.0787,0.2915,0.0125</t>
+  </si>
+  <si>
+    <t>0.8766,0.0006,0.1397,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.1714,0.0021,0.9710</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.8287,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9981,0.0035,0.0000</t>
+  </si>
+  <si>
+    <t>0.9158,0.0747,0.0099,0.0002</t>
+  </si>
+  <si>
+    <t>0.6693,0.2745,0.0194,0.0011</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0007,0.0002</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9421,0.0028,0.0470,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.0012,0.9958,0.0003</t>
-  </si>
-  <si>
-    <t>0.6901,0.0002,0.4721,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0001,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0001,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0188,0.9781,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.8660,0.0002,0.1647,0.0002</t>
-  </si>
-  <si>
-    <t>0.9532,0.0005,0.0452,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0007,0.9964,0.0006</t>
-  </si>
-  <si>
-    <t>0.0022,0.0004,0.9956,0.0004</t>
-  </si>
-  <si>
-    <t>0.2517,0.0001,0.8666,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9997,0.0005</t>
-  </si>
-  <si>
-    <t>0.8988,0.1053,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9194,0.0223,0.0250,0.0016</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9994,0.0028</t>
-  </si>
-  <si>
-    <t>0.0020,0.9902,0.0105,0.0002</t>
-  </si>
-  <si>
-    <t>0.9729,0.0117,0.0032,0.0041</t>
-  </si>
-  <si>
-    <t>0.9888,0.0020,0.0064,0.0009</t>
-  </si>
-  <si>
-    <t>0.5109,0.5923,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.0068,0.9818,0.0100,0.0019</t>
-  </si>
-  <si>
-    <t>0.0757,0.4734,0.2601,0.0092</t>
-  </si>
-  <si>
-    <t>0.0072,0.0026,0.9873,0.0004</t>
-  </si>
-  <si>
-    <t>0.0116,0.0047,0.9713,0.0014</t>
-  </si>
-  <si>
-    <t>0.0333,0.0001,0.9738,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0071,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9972,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9642,0.0008,0.7819</t>
-  </si>
-  <si>
-    <t>0.0005,0.9986,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0018,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0211,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0309,0.0009,0.9745,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0002,0.9975,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0032,0.9924,0.0003</t>
-  </si>
-  <si>
-    <t>0.9942,0.0044,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9988,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0019,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.9976,0.0008,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9817,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0024,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0008,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9857,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9977,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.1061,0.0021,0.9330,0.0001</t>
-  </si>
-  <si>
-    <t>0.9876,0.0070,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0013,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9962,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.7356,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9208,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9745,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0000,0.0029,0.9981</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.0005,0.9995</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.0001,0.9993</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.8159,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9952,0.9348,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.6070,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.8551,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9913,0.4921,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0007,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9937,0.0092,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0018,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.0128,0.9875,0.0004</t>
-  </si>
-  <si>
-    <t>0.9970,0.0001,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9982,0.0013</t>
-  </si>
-  <si>
-    <t>0.0004,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9985,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.9927,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.3106,0.7102,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.4257,0.0013,0.5430,0.0057</t>
-  </si>
-  <si>
-    <t>0.7530,0.0007,0.3302,0.0001</t>
-  </si>
-  <si>
-    <t>0.3963,0.0201,0.4193,0.0035</t>
-  </si>
-  <si>
-    <t>0.6347,0.0024,0.3527,0.0012</t>
-  </si>
-  <si>
-    <t>0.0013,0.0387,0.0032,0.9855</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0028</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9501,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.8851,0.0702,0.0338,0.0010</t>
-  </si>
-  <si>
-    <t>0.9154,0.0673,0.0094,0.0006</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9250,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.4316,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0070,0.0025,0.9889,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9404,0.0044,0.0391,0.0014</t>
+  </si>
+  <si>
+    <t>0.0791,0.0002,0.9446,0.0002</t>
+  </si>
+  <si>
+    <t>0.9676,0.0008,0.0205,0.0004</t>
+  </si>
+  <si>
+    <t>0.0374,0.0001,0.0002,0.9910</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9780,0.9787,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0032,0.9938,0.0010,0.0020</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.6168,0.4387,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.0000,0.0006,0.9989</t>
+  </si>
+  <si>
+    <t>0.9962,0.0008,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.0189,0.0295,0.9789,0.0010</t>
+  </si>
+  <si>
+    <t>0.9308,0.0006,0.0283,0.0091</t>
+  </si>
+  <si>
+    <t>0.9707,0.0001,0.0010,0.0191</t>
+  </si>
+  <si>
+    <t>0.8149,0.1774,0.0062,0.0006</t>
+  </si>
+  <si>
+    <t>0.9946,0.0005,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0022,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.1632,0.5767,0.0502,0.0006</t>
+  </si>
+  <si>
+    <t>0.8987,0.0071,0.0700,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0003,0.0003</t>
   </si>
   <si>
     <t>0.9993,0.0001,0.0001,0.0002</t>
   </si>
   <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9658,0.9824,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0252,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0090,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0099,0.0024,0.9885,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9386,0.0020,0.0557,0.0005</t>
-  </si>
-  <si>
-    <t>0.1103,0.0003,0.9221,0.0002</t>
-  </si>
-  <si>
-    <t>0.9534,0.0027,0.0261,0.0003</t>
-  </si>
-  <si>
-    <t>0.0090,0.0001,0.0001,0.9978</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9949,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9978,0.0006,0.0020</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.2407,0.7886,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0110,0.0000,0.0007,0.9956</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.0272,0.0397,0.9698,0.0029</t>
-  </si>
-  <si>
-    <t>0.8227,0.0002,0.0018,0.2069</t>
-  </si>
-  <si>
-    <t>0.9189,0.0036,0.0130,0.0356</t>
-  </si>
-  <si>
-    <t>0.0698,0.9305,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9902,0.0033,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.1558,0.2691,0.2410,0.0005</t>
-  </si>
-  <si>
-    <t>0.9734,0.0121,0.0070,0.0003</t>
-  </si>
-  <si>
-    <t>0.9928,0.0020,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0021,0.0009,0.0016</t>
+    <t>0.9992,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9886,0.0052,0.0009,0.0022</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.1423,0.8321,0.0028,0.0021</t>
+  </si>
+  <si>
+    <t>0.4446,0.5539,0.0098,0.0004</t>
+  </si>
+  <si>
+    <t>0.6820,0.3101,0.0060,0.0002</t>
+  </si>
+  <si>
+    <t>0.0516,0.0499,0.9365,0.0007</t>
+  </si>
+  <si>
+    <t>0.9941,0.0082,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9926,0.0020,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9701,0.0491,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.9901,0.0032,0.0025,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9989,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0128,0.0011,0.9907,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0013,0.9948,0.0007</t>
+  </si>
+  <si>
+    <t>0.0411,0.0005,0.9758,0.0001</t>
+  </si>
+  <si>
+    <t>0.0362,0.0160,0.9082,0.0014</t>
+  </si>
+  <si>
+    <t>0.1699,0.0811,0.5321,0.0003</t>
+  </si>
+  <si>
+    <t>0.0446,0.0696,0.8426,0.0008</t>
+  </si>
+  <si>
+    <t>0.5297,0.0023,0.5297,0.0002</t>
+  </si>
+  <si>
+    <t>0.9353,0.0032,0.0401,0.0009</t>
+  </si>
+  <si>
+    <t>0.0918,0.0082,0.8821,0.0034</t>
+  </si>
+  <si>
+    <t>0.0823,0.9439,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0602,0.9467,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.1201,0.9048,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.1203,0.9128,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.4583,0.6909,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.2634,0.6443,0.0114,0.0009</t>
+  </si>
+  <si>
+    <t>0.9798,0.0004,0.0151,0.0001</t>
+  </si>
+  <si>
+    <t>0.9755,0.0006,0.0124,0.0010</t>
+  </si>
+  <si>
+    <t>0.8644,0.0006,0.1501,0.0005</t>
+  </si>
+  <si>
+    <t>0.6576,0.0008,0.3331,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9992,0.0016</t>
+  </si>
+  <si>
+    <t>0.0057,0.0033,0.9851,0.0029</t>
+  </si>
+  <si>
+    <t>0.0104,0.1655,0.8998,0.0007</t>
+  </si>
+  <si>
+    <t>0.0471,0.0001,0.9744,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0249,0.9916,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.3250,0.6909,0.0016,0.0011</t>
-  </si>
-  <si>
-    <t>0.7937,0.2141,0.0064,0.0004</t>
-  </si>
-  <si>
-    <t>0.9846,0.0110,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.8698,0.0829,0.0319,0.0007</t>
-  </si>
-  <si>
-    <t>0.9937,0.0062,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0007,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0059,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0011,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.9904,0.0029,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.0009,0.0087,0.9963,0.0015</t>
-  </si>
-  <si>
-    <t>0.0012,0.0003,0.9978,0.0005</t>
-  </si>
-  <si>
-    <t>0.0125,0.0140,0.9854,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.0036,0.9868,0.0012</t>
-  </si>
-  <si>
-    <t>0.0058,0.0003,0.9954,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.0418,0.9656,0.0023</t>
-  </si>
-  <si>
-    <t>0.1015,0.0700,0.6931,0.0004</t>
-  </si>
-  <si>
-    <t>0.0440,0.0156,0.9167,0.0007</t>
-  </si>
-  <si>
-    <t>0.3652,0.0090,0.5991,0.0012</t>
-  </si>
-  <si>
-    <t>0.7595,0.0017,0.2478,0.0012</t>
-  </si>
-  <si>
-    <t>0.0623,0.0005,0.9512,0.0005</t>
-  </si>
-  <si>
-    <t>0.3211,0.7594,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0096,0.9916,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.6925,0.3671,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.5751,0.5676,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0101,0.9913,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.3621,0.0347,0.3665,0.0023</t>
-  </si>
-  <si>
-    <t>0.9386,0.0005,0.0713,0.0001</t>
-  </si>
-  <si>
-    <t>0.8865,0.0034,0.0500,0.0193</t>
-  </si>
-  <si>
-    <t>0.9526,0.0003,0.0548,0.0001</t>
-  </si>
-  <si>
-    <t>0.1652,0.0003,0.8886,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9992,0.0013</t>
-  </si>
-  <si>
-    <t>0.0006,0.0036,0.9941,0.0078</t>
-  </si>
-  <si>
-    <t>0.0252,0.0307,0.9429,0.0013</t>
-  </si>
-  <si>
-    <t>0.0108,0.0006,0.9879,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.0023,0.9971,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0039,0.9978,0.0012</t>
-  </si>
-  <si>
-    <t>0.2336,0.1326,0.4752,0.0047</t>
-  </si>
-  <si>
-    <t>0.9755,0.0003,0.0113,0.0025</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0909,0.9835,0.0008</t>
-  </si>
-  <si>
-    <t>0.0075,0.0006,0.9937,0.0000</t>
-  </si>
-  <si>
-    <t>0.0220,0.0001,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0033,0.9917,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.0851,0.9986,0.0005</t>
-  </si>
-  <si>
-    <t>0.8161,0.0001,0.2450,0.0001</t>
-  </si>
-  <si>
-    <t>0.8646,0.0002,0.1754,0.0002</t>
-  </si>
-  <si>
-    <t>0.9741,0.0001,0.0251,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0017,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0006,0.9956,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0026,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.0421,0.9564,0.0020</t>
-  </si>
-  <si>
-    <t>0.0043,0.0020,0.9890,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0303,0.0015,0.9572,0.0041</t>
-  </si>
-  <si>
-    <t>0.0366,0.0031,0.9522,0.0020</t>
-  </si>
-  <si>
-    <t>0.0304,0.0017,0.9570,0.0049</t>
-  </si>
-  <si>
-    <t>0.8862,0.0000,0.0005,0.1472</t>
-  </si>
-  <si>
-    <t>0.0028,0.0046,0.0002,0.9971</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.0039,0.9986</t>
-  </si>
-  <si>
-    <t>0.9393,0.0020,0.0012,0.0208</t>
+    <t>0.0013,0.0028,0.9975,0.0017</t>
+  </si>
+  <si>
+    <t>0.1071,0.4330,0.2414,0.0044</t>
+  </si>
+  <si>
+    <t>0.8389,0.0002,0.0959,0.0076</t>
+  </si>
+  <si>
+    <t>0.0024,0.0004,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0484,0.9949,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.0001,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0243,0.0030,0.9715,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0069,0.0009,0.9870,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0640,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0000,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.8317,0.0003,0.1989,0.0004</t>
+  </si>
+  <si>
+    <t>0.8993,0.0001,0.1379,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0026,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0050,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0252,0.0021,0.9673,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0039,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0061,0.0102,0.9754,0.0020</t>
+  </si>
+  <si>
+    <t>0.0047,0.0118,0.9694,0.0019</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0070,0.0008,0.9894,0.0027</t>
+  </si>
+  <si>
+    <t>0.0767,0.0018,0.9189,0.0017</t>
+  </si>
+  <si>
+    <t>0.0051,0.0004,0.9841,0.0072</t>
+  </si>
+  <si>
+    <t>0.9930,0.0000,0.0001,0.0052</t>
+  </si>
+  <si>
+    <t>0.0020,0.0153,0.0002,0.9969</t>
+  </si>
+  <si>
+    <t>0.0122,0.0003,0.0056,0.9928</t>
+  </si>
+  <si>
+    <t>0.4894,0.0522,0.0068,0.1815</t>
   </si>
 </sst>
 </file>
@@ -1872,7 +1896,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1886,7 +1910,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1900,7 +1924,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1914,7 +1938,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1928,7 +1952,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1942,7 +1966,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1956,7 +1980,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1970,7 +1994,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1984,7 +2008,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1998,7 +2022,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2012,7 +2036,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2026,7 +2050,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2037,10 +2061,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2054,7 +2078,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2065,10 +2089,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2082,7 +2106,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2096,7 +2120,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2110,7 +2134,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2124,7 +2148,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2138,7 +2162,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2152,7 +2176,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2166,7 +2190,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2180,7 +2204,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2194,7 +2218,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2208,7 +2232,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2222,7 +2246,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2236,7 +2260,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2250,7 +2274,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2264,7 +2288,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2275,10 +2299,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2292,7 +2316,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2306,7 +2330,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2320,7 +2344,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2334,7 +2358,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2348,7 +2372,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2362,7 +2386,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2376,7 +2400,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2387,10 +2411,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2404,7 +2428,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2418,7 +2442,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2432,7 +2456,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2446,7 +2470,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2460,7 +2484,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2474,7 +2498,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2485,10 +2509,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2502,7 +2526,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2516,7 +2540,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2530,7 +2554,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2544,7 +2568,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2558,7 +2582,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2572,7 +2596,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2586,7 +2610,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2600,7 +2624,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2614,7 +2638,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2628,7 +2652,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2642,7 +2666,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2656,7 +2680,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2670,7 +2694,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2684,7 +2708,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2698,7 +2722,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>271</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2712,7 +2736,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2726,7 +2750,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2740,7 +2764,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2754,7 +2778,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2768,7 +2792,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2782,7 +2806,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2796,7 +2820,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2810,7 +2834,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2824,7 +2848,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2838,7 +2862,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2852,7 +2876,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2866,7 +2890,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2880,7 +2904,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2891,10 +2915,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2908,7 +2932,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2922,7 +2946,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2936,7 +2960,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2950,7 +2974,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2964,7 +2988,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2978,7 +3002,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2992,7 +3016,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3006,7 +3030,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3020,7 +3044,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3034,7 +3058,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3045,10 +3069,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3059,10 +3083,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3073,10 +3097,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3090,7 +3114,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3104,7 +3128,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3118,7 +3142,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3132,7 +3156,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3146,7 +3170,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>274</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3160,7 +3184,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>270</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3174,7 +3198,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3188,7 +3212,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3202,7 +3226,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3216,7 +3240,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3230,7 +3254,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3244,7 +3268,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3258,7 +3282,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>351</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3272,7 +3296,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3286,7 +3310,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>272</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3300,7 +3324,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3314,7 +3338,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3328,7 +3352,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3342,7 +3366,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3356,7 +3380,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3370,7 +3394,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3384,7 +3408,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3398,7 +3422,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3412,7 +3436,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3426,7 +3450,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3440,7 +3464,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>362</v>
+        <v>312</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3454,7 +3478,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3468,7 +3492,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3482,7 +3506,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3493,10 +3517,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,7 +3534,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3524,7 +3548,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3538,7 +3562,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3552,7 +3576,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3566,7 +3590,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3580,7 +3604,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3594,7 +3618,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3608,7 +3632,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3622,7 +3646,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3636,7 +3660,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3650,7 +3674,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3664,7 +3688,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3678,7 +3702,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3692,7 +3716,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>270</v>
+        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3706,7 +3730,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3720,7 +3744,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3734,7 +3758,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3748,7 +3772,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3762,7 +3786,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3776,7 +3800,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3790,7 +3814,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3804,7 +3828,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3818,7 +3842,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3832,7 +3856,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3846,7 +3870,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3860,7 +3884,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3874,7 +3898,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3888,7 +3912,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3902,7 +3926,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3916,7 +3940,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3930,7 +3954,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3944,7 +3968,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3958,7 +3982,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3969,10 +3993,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3986,7 +4010,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4000,7 +4024,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4014,7 +4038,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4028,7 +4052,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4042,7 +4066,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4056,7 +4080,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4067,10 +4091,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4084,7 +4108,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4098,7 +4122,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4109,10 +4133,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4126,7 +4150,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4140,7 +4164,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4154,7 +4178,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>410</v>
+        <v>355</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4168,7 +4192,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4182,7 +4206,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4196,7 +4220,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4210,7 +4234,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4224,7 +4248,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4238,7 +4262,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4252,7 +4276,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4266,7 +4290,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4277,10 +4301,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4294,7 +4318,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4305,10 +4329,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4322,7 +4346,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4336,7 +4360,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4350,7 +4374,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4364,7 +4388,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4378,7 +4402,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4392,7 +4416,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4406,7 +4430,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>326</v>
+        <v>433</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4420,7 +4444,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4434,7 +4458,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4448,7 +4472,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4462,7 +4486,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4476,7 +4500,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>353</v>
+        <v>437</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4490,7 +4514,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4504,7 +4528,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4518,7 +4542,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4532,7 +4556,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,7 +4570,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4560,7 +4584,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4571,10 +4595,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4588,7 +4612,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4602,7 +4626,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4616,7 +4640,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4630,7 +4654,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4641,10 +4665,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4658,7 +4682,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4672,7 +4696,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4683,10 +4707,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4700,7 +4724,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4714,7 +4738,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4728,7 +4752,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4739,10 +4763,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4756,7 +4780,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4770,7 +4794,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4784,7 +4808,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4798,7 +4822,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4812,7 +4836,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4826,7 +4850,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4840,7 +4864,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4854,7 +4878,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4868,7 +4892,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4882,7 +4906,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4896,7 +4920,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4910,7 +4934,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4924,7 +4948,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>416</v>
+        <v>469</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4938,7 +4962,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4949,10 +4973,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4966,7 +4990,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4980,7 +5004,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4994,7 +5018,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>431</v>
+        <v>474</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5008,7 +5032,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5022,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5036,7 +5060,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5050,7 +5074,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5064,7 +5088,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5078,7 +5102,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5092,7 +5116,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5106,7 +5130,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5120,7 +5144,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5134,7 +5158,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>474</v>
+        <v>271</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5148,7 +5172,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5162,7 +5186,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5176,7 +5200,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5190,7 +5214,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5204,7 +5228,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5218,7 +5242,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5232,7 +5256,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>478</v>
+        <v>271</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5246,7 +5270,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5260,7 +5284,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5274,7 +5298,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5288,7 +5312,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5302,7 +5326,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5316,7 +5340,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5330,7 +5354,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5344,7 +5368,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5358,7 +5382,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5372,7 +5396,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5386,7 +5410,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5400,7 +5424,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5414,7 +5438,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5425,10 +5449,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D256" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
